--- a/BillReady_2.0_Prioritized_Backlog.xlsx
+++ b/BillReady_2.0_Prioritized_Backlog.xlsx
@@ -971,7 +971,7 @@
       </c>
       <c r="K7" s="24" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="K8" s="24" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="K9" s="24" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="K10" s="24" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>

--- a/BillReady_2.0_Prioritized_Backlog.xlsx
+++ b/BillReady_2.0_Prioritized_Backlog.xlsx
@@ -1236,7 +1236,7 @@
       </c>
       <c r="K12" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="K13" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="K14" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="K19" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="K20" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="K22" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="K23" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>

--- a/BillReady_2.0_Prioritized_Backlog.xlsx
+++ b/BillReady_2.0_Prioritized_Backlog.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -112,8 +112,11 @@
       <color rgb="FF0B8B68"/>
       <sz val="12"/>
     </font>
+    <font>
+      <color rgb="00276221"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -148,6 +151,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF3F4F6"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -185,7 +194,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -312,6 +321,9 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -757,9 +769,9 @@
           <t>BillNumberService uses an in-memory counter. Two devices can generate the same bill number simultaneously, and dedup on sync silently drops one bill. Fix: Create a Supabase Edge Function or DB sequence that atomically generates bill numbers per business. Call it from completeBill() before saving. Remove client-side counter as primary source.</t>
         </is>
       </c>
-      <c r="K3" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K3" s="43" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -810,9 +822,9 @@
           <t>canAddBill is checked client-side only; trivially bypassable. increment_bill_count RPC runs AFTER bill creation. Fix: Move bill count check to a Supabase Edge Function or RLS policy that rejects inserts when limit is reached. Return error to client if limit exceeded.</t>
         </is>
       </c>
-      <c r="K4" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K4" s="43" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -916,9 +928,9 @@
           <t>completeBill() saves the bill, THEN decrements stock, THEN updates credit. If app crashes between steps, data is inconsistent. Fix: Use Supabase RPC function that atomically: (1) saves bill, (2) decrements stock, (3) updates credit, (4) increments bill count. If any step fails, all roll back.</t>
         </is>
       </c>
-      <c r="K6" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K6" s="43" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -1181,9 +1193,9 @@
           <t>Product.stockQuantity, Customer.outstandingBalance/advanceBalance, Supplier.outstandingPayable, LineItem.quantity/discountPercent, SerialNumber.status/billId, JobLineItem.quantity/unitPrice are mutable. State can change without notifyListeners(). Fix: Make all fields final. Add copyWith() where missing. Update providers to create new instances instead of mutating.</t>
         </is>
       </c>
-      <c r="K11" s="26" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K11" s="43" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -1393,9 +1405,9 @@
           <t>PermissionService checks are client-side only. A modified client can bypass all role restrictions. Fix: Create Supabase RLS policies that check user role stored in app_users table. E.g., only owner role can delete bills, only owner/manager can adjust stock.</t>
         </is>
       </c>
-      <c r="K15" s="26" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K15" s="43" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -1446,9 +1458,9 @@
           <t>app_state.json stored unencrypted with all business data and PII. Fix: Use flutter_secure_storage for encryption key, encrypt state JSON with AES before writing. Decrypt on read. Consider using Hive with encryption instead of raw file I/O.</t>
         </is>
       </c>
-      <c r="K16" s="26" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K16" s="43" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -1499,9 +1511,9 @@
           <t>_asDouble(), _asInt(), _nullableInt(), _nullableDouble(), _nullableString() duplicated across 15+ model files. Fix: Create a shared JsonHelpers class with static methods. Update all models to use the shared helpers.</t>
         </is>
       </c>
-      <c r="K17" s="26" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K17" s="43" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -1552,9 +1564,9 @@
           <t>Three separate payment mode enums: PaymentMode (4 values), ExpensePaymentMode (4 values), SettlementPaymentMode (3 values). Confusing and error-prone. Fix: Create a single unified PaymentMethod enum with all modes. Add a "context" or "applicability" concept if some modes only apply in certain scenarios.</t>
         </is>
       </c>
-      <c r="K18" s="26" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K18" s="43" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -1711,9 +1723,9 @@
           <t>No crash reporting. Production crashes are invisible. Fix: Integrate Sentry (sentry_flutter) or Firebase Crashlytics. Wrap runApp in error zone. Configure breadcrumbs for state changes.</t>
         </is>
       </c>
-      <c r="K21" s="26" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="K21" s="43" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
     </row>

--- a/BillReady_2.0_Prioritized_Backlog.xlsx
+++ b/BillReady_2.0_Prioritized_Backlog.xlsx
@@ -1990,7 +1990,7 @@
       </c>
       <c r="K26" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="K27" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="K28" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="K29" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="K30" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="K31" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="K32" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="K33" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="K36" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="K37" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="K38" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="K39" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="K40" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>N/A - crypto is used for PIN hashing</t>
         </is>
       </c>
     </row>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="K41" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="K42" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="K45" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="K46" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="K47" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="K48" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="K49" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
       </c>
       <c r="K50" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="K53" s="30" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="K54" s="30" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="K55" s="30" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="K56" s="30" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -3633,7 +3633,7 @@
       </c>
       <c r="K57" s="30" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="K58" s="30" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="K59" s="30" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="K60" s="30" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -3845,7 +3845,7 @@
       </c>
       <c r="K61" s="30" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="K62" s="30" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="K63" s="30" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="K64" s="30" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -4057,7 +4057,7 @@
       </c>
       <c r="K65" s="30" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
@@ -4110,7 +4110,7 @@
       </c>
       <c r="K66" s="30" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
     </row>
